--- a/panchang-data/Kedarnath2026.xlsx
+++ b/panchang-data/Kedarnath2026.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5392">
   <si>
     <t>दिनाङ्क</t>
   </si>
@@ -16201,6 +16201,9 @@
   </si>
   <si>
     <t>121°05'03.31</t>
+  </si>
+  <si>
+    <t>ज्येष्ठ अधिक</t>
   </si>
 </sst>
 </file>
@@ -16690,7 +16693,7 @@
         <v>46023</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>29</v>
@@ -16776,7 +16779,7 @@
         <v>46024</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>50</v>
@@ -16862,7 +16865,7 @@
         <v>46025</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>70</v>
@@ -16948,7 +16951,7 @@
         <v>46026</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>88</v>
+        <v>561</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>89</v>
@@ -17034,7 +17037,7 @@
         <v>46027</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>88</v>
+        <v>561</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>108</v>
@@ -17120,7 +17123,7 @@
         <v>46028</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>88</v>
+        <v>561</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>125</v>
@@ -17206,7 +17209,7 @@
         <v>46029</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>88</v>
+        <v>561</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>143</v>
@@ -17292,7 +17295,7 @@
         <v>46030</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>88</v>
+        <v>561</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>29</v>
@@ -17378,7 +17381,7 @@
         <v>46031</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>88</v>
+        <v>561</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>50</v>
@@ -17464,7 +17467,7 @@
         <v>46032</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>88</v>
+        <v>561</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>70</v>
@@ -17550,7 +17553,7 @@
         <v>46033</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>88</v>
+        <v>561</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>89</v>
@@ -17636,7 +17639,7 @@
         <v>46034</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>88</v>
+        <v>561</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>108</v>
@@ -17722,7 +17725,7 @@
         <v>46035</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>88</v>
+        <v>561</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>125</v>
@@ -17808,7 +17811,7 @@
         <v>46036</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>88</v>
+        <v>561</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>143</v>
@@ -17894,7 +17897,7 @@
         <v>46037</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>88</v>
+        <v>561</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>29</v>
@@ -17980,7 +17983,7 @@
         <v>46038</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>88</v>
+        <v>561</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>50</v>
@@ -18066,7 +18069,7 @@
         <v>46039</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>88</v>
+        <v>561</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>70</v>
@@ -18152,7 +18155,7 @@
         <v>46040</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>88</v>
+        <v>561</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>89</v>
@@ -18238,7 +18241,7 @@
         <v>46041</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>88</v>
+        <v>561</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>108</v>
@@ -18324,7 +18327,7 @@
         <v>46042</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>88</v>
+        <v>561</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>125</v>
@@ -18410,7 +18413,7 @@
         <v>46043</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>88</v>
+        <v>561</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>143</v>
@@ -18496,7 +18499,7 @@
         <v>46044</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>88</v>
+        <v>561</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>29</v>
@@ -18582,7 +18585,7 @@
         <v>46045</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>88</v>
+        <v>561</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>50</v>
@@ -18668,7 +18671,7 @@
         <v>46046</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>88</v>
+        <v>561</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>70</v>
@@ -18754,7 +18757,7 @@
         <v>46047</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>88</v>
+        <v>561</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>89</v>
@@ -18840,7 +18843,7 @@
         <v>46048</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>88</v>
+        <v>561</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>108</v>
@@ -18926,7 +18929,7 @@
         <v>46049</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>88</v>
+        <v>561</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>125</v>
@@ -19012,7 +19015,7 @@
         <v>46050</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>88</v>
+        <v>561</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>143</v>
@@ -19098,7 +19101,7 @@
         <v>46051</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>88</v>
+        <v>561</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>29</v>
@@ -19184,7 +19187,7 @@
         <v>46052</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>88</v>
+        <v>561</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>50</v>
@@ -19270,7 +19273,7 @@
         <v>46053</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>88</v>
+        <v>561</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>70</v>
@@ -19356,7 +19359,7 @@
         <v>46054</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>88</v>
+        <v>561</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>89</v>
@@ -19442,7 +19445,7 @@
         <v>46055</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>561</v>
+        <v>1003</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>108</v>
@@ -19528,7 +19531,7 @@
         <v>46056</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>561</v>
+        <v>1003</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>125</v>
@@ -19614,7 +19617,7 @@
         <v>46057</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>561</v>
+        <v>1003</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>143</v>
@@ -19700,7 +19703,7 @@
         <v>46058</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>561</v>
+        <v>1003</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>29</v>
@@ -19786,7 +19789,7 @@
         <v>46059</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>561</v>
+        <v>1003</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>50</v>
@@ -19872,7 +19875,7 @@
         <v>46060</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>561</v>
+        <v>1003</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>70</v>
@@ -19958,7 +19961,7 @@
         <v>46061</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>561</v>
+        <v>1003</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>89</v>
@@ -20044,7 +20047,7 @@
         <v>46062</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>561</v>
+        <v>1003</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>108</v>
@@ -20130,7 +20133,7 @@
         <v>46063</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>561</v>
+        <v>1003</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>125</v>
@@ -20216,7 +20219,7 @@
         <v>46064</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>561</v>
+        <v>1003</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>143</v>
@@ -20302,7 +20305,7 @@
         <v>46065</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>561</v>
+        <v>1003</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>29</v>
@@ -20388,7 +20391,7 @@
         <v>46066</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>561</v>
+        <v>1003</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>50</v>
@@ -20474,7 +20477,7 @@
         <v>46067</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>561</v>
+        <v>1003</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>70</v>
@@ -20560,7 +20563,7 @@
         <v>46068</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>561</v>
+        <v>1003</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>89</v>
@@ -20646,7 +20649,7 @@
         <v>46069</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>561</v>
+        <v>1003</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>108</v>
@@ -20732,7 +20735,7 @@
         <v>46070</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>561</v>
+        <v>1003</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>125</v>
@@ -20818,7 +20821,7 @@
         <v>46071</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>561</v>
+        <v>1003</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>143</v>
@@ -20904,7 +20907,7 @@
         <v>46072</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>561</v>
+        <v>1003</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>29</v>
@@ -20990,7 +20993,7 @@
         <v>46073</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>561</v>
+        <v>1003</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>50</v>
@@ -21076,7 +21079,7 @@
         <v>46074</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>561</v>
+        <v>1003</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>70</v>
@@ -21162,7 +21165,7 @@
         <v>46075</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>561</v>
+        <v>1003</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>89</v>
@@ -21248,7 +21251,7 @@
         <v>46076</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>561</v>
+        <v>1003</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>108</v>
@@ -21334,7 +21337,7 @@
         <v>46077</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>561</v>
+        <v>1003</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>125</v>
@@ -21420,7 +21423,7 @@
         <v>46078</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>561</v>
+        <v>1003</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>143</v>
@@ -21506,7 +21509,7 @@
         <v>46079</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>561</v>
+        <v>1003</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>29</v>
@@ -21592,7 +21595,7 @@
         <v>46080</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>561</v>
+        <v>1003</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>50</v>
@@ -21678,7 +21681,7 @@
         <v>46081</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>561</v>
+        <v>1003</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>70</v>
@@ -21764,7 +21767,7 @@
         <v>46082</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>561</v>
+        <v>1003</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>89</v>
@@ -21850,7 +21853,7 @@
         <v>46083</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>561</v>
+        <v>1003</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>108</v>
@@ -21936,7 +21939,7 @@
         <v>46084</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>561</v>
+        <v>1003</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>125</v>
@@ -22022,7 +22025,7 @@
         <v>46085</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>1003</v>
+        <v>1444</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>143</v>
@@ -22108,7 +22111,7 @@
         <v>46086</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>1003</v>
+        <v>1444</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>29</v>
@@ -22194,7 +22197,7 @@
         <v>46087</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>1003</v>
+        <v>1444</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>50</v>
@@ -22280,7 +22283,7 @@
         <v>46088</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>1003</v>
+        <v>1444</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>70</v>
@@ -22366,7 +22369,7 @@
         <v>46089</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>1003</v>
+        <v>1444</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>89</v>
@@ -22452,7 +22455,7 @@
         <v>46090</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>1003</v>
+        <v>1444</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>108</v>
@@ -22538,7 +22541,7 @@
         <v>46091</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>1003</v>
+        <v>1444</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>125</v>
@@ -22624,7 +22627,7 @@
         <v>46092</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>1003</v>
+        <v>1444</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>143</v>
@@ -22710,7 +22713,7 @@
         <v>46093</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>1003</v>
+        <v>1444</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>29</v>
@@ -22796,7 +22799,7 @@
         <v>46094</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>1003</v>
+        <v>1444</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>50</v>
@@ -22882,7 +22885,7 @@
         <v>46095</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>1003</v>
+        <v>1444</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>70</v>
@@ -22968,7 +22971,7 @@
         <v>46096</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>1003</v>
+        <v>1444</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>89</v>
@@ -23054,7 +23057,7 @@
         <v>46097</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>1003</v>
+        <v>1444</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>108</v>
@@ -23140,7 +23143,7 @@
         <v>46098</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>1003</v>
+        <v>1444</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>125</v>
@@ -23226,7 +23229,7 @@
         <v>46099</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>1003</v>
+        <v>1444</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>143</v>
@@ -23312,7 +23315,7 @@
         <v>46100</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>1003</v>
+        <v>1444</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>29</v>
@@ -23398,7 +23401,7 @@
         <v>46101</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>1003</v>
+        <v>1444</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>50</v>
@@ -23484,7 +23487,7 @@
         <v>46102</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>1003</v>
+        <v>1444</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>70</v>
@@ -23570,7 +23573,7 @@
         <v>46103</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>1003</v>
+        <v>1444</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>89</v>
@@ -23656,7 +23659,7 @@
         <v>46104</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>1003</v>
+        <v>1444</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>108</v>
@@ -23742,7 +23745,7 @@
         <v>46105</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>1003</v>
+        <v>1444</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>125</v>
@@ -23828,7 +23831,7 @@
         <v>46106</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>1003</v>
+        <v>1444</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>143</v>
@@ -23914,7 +23917,7 @@
         <v>46107</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>1003</v>
+        <v>1444</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>29</v>
@@ -24000,7 +24003,7 @@
         <v>46108</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>1003</v>
+        <v>1444</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>50</v>
@@ -24086,7 +24089,7 @@
         <v>46109</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>1003</v>
+        <v>1444</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>70</v>
@@ -24172,7 +24175,7 @@
         <v>46110</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>1003</v>
+        <v>1444</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>89</v>
@@ -24258,7 +24261,7 @@
         <v>46111</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>1003</v>
+        <v>1444</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>108</v>
@@ -24344,7 +24347,7 @@
         <v>46112</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>1003</v>
+        <v>1444</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>125</v>
@@ -24430,7 +24433,7 @@
         <v>46113</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>1003</v>
+        <v>1444</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>143</v>
@@ -24516,7 +24519,7 @@
         <v>46114</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>1003</v>
+        <v>1444</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>29</v>
@@ -24602,7 +24605,7 @@
         <v>46115</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>1444</v>
+        <v>1866</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>50</v>
@@ -24688,7 +24691,7 @@
         <v>46116</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>1444</v>
+        <v>1866</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>70</v>
@@ -24774,7 +24777,7 @@
         <v>46117</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>1444</v>
+        <v>1866</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>89</v>
@@ -24860,7 +24863,7 @@
         <v>46118</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>1444</v>
+        <v>1866</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>108</v>
@@ -24946,7 +24949,7 @@
         <v>46119</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>1444</v>
+        <v>1866</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>125</v>
@@ -25032,7 +25035,7 @@
         <v>46120</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>1444</v>
+        <v>1866</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>143</v>
@@ -25118,7 +25121,7 @@
         <v>46121</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>1444</v>
+        <v>1866</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>29</v>
@@ -25204,7 +25207,7 @@
         <v>46122</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>1444</v>
+        <v>1866</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>50</v>
@@ -25290,7 +25293,7 @@
         <v>46123</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>1444</v>
+        <v>1866</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>70</v>
@@ -25376,7 +25379,7 @@
         <v>46124</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>1444</v>
+        <v>1866</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>89</v>
@@ -25462,7 +25465,7 @@
         <v>46125</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>1444</v>
+        <v>1866</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>108</v>
@@ -25548,7 +25551,7 @@
         <v>46126</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>1444</v>
+        <v>1866</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>125</v>
@@ -25634,7 +25637,7 @@
         <v>46127</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>1444</v>
+        <v>1866</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>143</v>
@@ -25720,7 +25723,7 @@
         <v>46128</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>1444</v>
+        <v>1866</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>29</v>
@@ -25806,7 +25809,7 @@
         <v>46129</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>1444</v>
+        <v>1866</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>50</v>
@@ -25892,7 +25895,7 @@
         <v>46130</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>1444</v>
+        <v>1866</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>70</v>
@@ -25978,7 +25981,7 @@
         <v>46131</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>1444</v>
+        <v>1866</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>89</v>
@@ -26064,7 +26067,7 @@
         <v>46132</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>1444</v>
+        <v>1866</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>108</v>
@@ -26150,7 +26153,7 @@
         <v>46133</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>1444</v>
+        <v>1866</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>125</v>
@@ -26236,7 +26239,7 @@
         <v>46134</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>1444</v>
+        <v>1866</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>143</v>
@@ -26322,7 +26325,7 @@
         <v>46135</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>1444</v>
+        <v>1866</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>29</v>
@@ -26408,7 +26411,7 @@
         <v>46136</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>1444</v>
+        <v>1866</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>50</v>
@@ -26494,7 +26497,7 @@
         <v>46137</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>1444</v>
+        <v>1866</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>70</v>
@@ -26580,7 +26583,7 @@
         <v>46138</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>1444</v>
+        <v>1866</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>89</v>
@@ -26666,7 +26669,7 @@
         <v>46139</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>1444</v>
+        <v>1866</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>108</v>
@@ -26752,7 +26755,7 @@
         <v>46140</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>1444</v>
+        <v>1866</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>125</v>
@@ -26838,7 +26841,7 @@
         <v>46141</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>1444</v>
+        <v>1866</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>143</v>
@@ -26924,7 +26927,7 @@
         <v>46142</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>1444</v>
+        <v>1866</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>29</v>
@@ -27010,7 +27013,7 @@
         <v>46143</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>1444</v>
+        <v>1866</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>50</v>
@@ -27096,7 +27099,7 @@
         <v>46144</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>1866</v>
+        <v>2303</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>70</v>
@@ -27182,7 +27185,7 @@
         <v>46145</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>1866</v>
+        <v>2303</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>89</v>
@@ -27268,7 +27271,7 @@
         <v>46146</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>1866</v>
+        <v>2303</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>108</v>
@@ -27354,7 +27357,7 @@
         <v>46147</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>1866</v>
+        <v>2303</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>125</v>
@@ -27440,7 +27443,7 @@
         <v>46148</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>1866</v>
+        <v>2303</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>143</v>
@@ -27526,7 +27529,7 @@
         <v>46149</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>1866</v>
+        <v>2303</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>29</v>
@@ -27612,7 +27615,7 @@
         <v>46150</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>1866</v>
+        <v>2303</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>50</v>
@@ -27698,7 +27701,7 @@
         <v>46151</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>1866</v>
+        <v>2303</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>70</v>
@@ -27784,7 +27787,7 @@
         <v>46152</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>1866</v>
+        <v>2303</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>89</v>
@@ -27870,7 +27873,7 @@
         <v>46153</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>1866</v>
+        <v>2303</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>108</v>
@@ -27956,7 +27959,7 @@
         <v>46154</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>1866</v>
+        <v>2303</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>125</v>
@@ -28042,7 +28045,7 @@
         <v>46155</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>1866</v>
+        <v>2303</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>143</v>
@@ -28128,7 +28131,7 @@
         <v>46156</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>1866</v>
+        <v>2303</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>29</v>
@@ -28214,7 +28217,7 @@
         <v>46157</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>1866</v>
+        <v>2303</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>50</v>
@@ -28300,7 +28303,7 @@
         <v>46158</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>1866</v>
+        <v>2303</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>70</v>
@@ -28386,7 +28389,7 @@
         <v>46159</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>1866</v>
+        <v>5391</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>89</v>
@@ -28472,7 +28475,7 @@
         <v>46160</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>1866</v>
+        <v>5391</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>108</v>
@@ -28558,7 +28561,7 @@
         <v>46161</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>1866</v>
+        <v>5391</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>125</v>
@@ -28644,7 +28647,7 @@
         <v>46162</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>1866</v>
+        <v>5391</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>143</v>
@@ -28730,7 +28733,7 @@
         <v>46163</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>1866</v>
+        <v>5391</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>29</v>
@@ -28816,7 +28819,7 @@
         <v>46164</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>1866</v>
+        <v>5391</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>50</v>
@@ -28902,7 +28905,7 @@
         <v>46165</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>1866</v>
+        <v>5391</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>70</v>
@@ -28988,7 +28991,7 @@
         <v>46166</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>1866</v>
+        <v>5391</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>89</v>
@@ -29074,7 +29077,7 @@
         <v>46167</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>1866</v>
+        <v>5391</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>108</v>
@@ -29160,7 +29163,7 @@
         <v>46168</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>1866</v>
+        <v>5391</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>125</v>
@@ -29246,7 +29249,7 @@
         <v>46169</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>1866</v>
+        <v>5391</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>143</v>
@@ -29332,7 +29335,7 @@
         <v>46170</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>1866</v>
+        <v>5391</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>29</v>
@@ -29418,7 +29421,7 @@
         <v>46171</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>1866</v>
+        <v>5391</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>50</v>
@@ -29504,7 +29507,7 @@
         <v>46172</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>1866</v>
+        <v>5391</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>70</v>
@@ -29590,7 +29593,7 @@
         <v>46173</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>1866</v>
+        <v>5391</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>89</v>
@@ -29676,7 +29679,7 @@
         <v>46174</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>2303</v>
+        <v>5391</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>108</v>
@@ -29762,7 +29765,7 @@
         <v>46175</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>2303</v>
+        <v>5391</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>125</v>
@@ -29848,7 +29851,7 @@
         <v>46176</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>2303</v>
+        <v>5391</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>143</v>
@@ -29934,7 +29937,7 @@
         <v>46177</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>2303</v>
+        <v>5391</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>29</v>
@@ -30020,7 +30023,7 @@
         <v>46178</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>2303</v>
+        <v>5391</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>50</v>
@@ -30106,7 +30109,7 @@
         <v>46179</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>2303</v>
+        <v>5391</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>70</v>
@@ -30192,7 +30195,7 @@
         <v>46180</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>2303</v>
+        <v>5391</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>89</v>
@@ -30278,7 +30281,7 @@
         <v>46181</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>2303</v>
+        <v>5391</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>108</v>
@@ -30364,7 +30367,7 @@
         <v>46182</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>2303</v>
+        <v>5391</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>125</v>
@@ -30450,7 +30453,7 @@
         <v>46183</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>2303</v>
+        <v>5391</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>143</v>
@@ -30536,7 +30539,7 @@
         <v>46184</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>2303</v>
+        <v>5391</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>29</v>
@@ -30622,7 +30625,7 @@
         <v>46185</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>2303</v>
+        <v>5391</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>50</v>
@@ -30708,7 +30711,7 @@
         <v>46186</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>2303</v>
+        <v>5391</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>70</v>
@@ -30794,7 +30797,7 @@
         <v>46187</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>2303</v>
+        <v>5391</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>89</v>
@@ -30880,7 +30883,7 @@
         <v>46188</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>2303</v>
+        <v>5391</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>108</v>
